--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.17.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.17.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -823,7 +823,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.17.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.17.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y28"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="39" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.17.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.17.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0017.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0017.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -597,16 +597,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L12: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œAnd, w</t>
+          <t>L69: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L19: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: Chancery of the late Province of Upper Canada.â€�</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]10 THE STATUTES.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]10 THE STATUTES.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L20: isolated marker/symbol line :: /</t>
@@ -641,7 +645,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -650,14 +654,10 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L13: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œsugges</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: " same â‚¬</t>
+          <t>L54: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: " same €</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -701,11 +701,7 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L16: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œcosts o</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
@@ -734,7 +730,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -748,17 +744,13 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œthe</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L69: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr"/>
@@ -795,11 +787,7 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L18: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œthe pw</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
@@ -842,11 +830,7 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L19: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œthe</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
@@ -889,11 +873,7 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L22: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œvested</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
@@ -932,11 +912,7 @@
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œmake</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
@@ -961,7 +937,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -975,11 +951,7 @@
       <c r="G10" s="1" t="inlineStr"/>
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: by the 12th Vic. Ch.64, intitled â€œAn Act for the more</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
@@ -1009,7 +981,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1018,11 +990,7 @@
       <c r="G11" s="1" t="inlineStr"/>
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of the Chancery Commissioners, and that â€œWhereas the</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
@@ -1061,11 +1029,7 @@
       <c r="G12" s="1" t="inlineStr"/>
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr"/>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œcarryin</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
@@ -1104,11 +1068,7 @@
       <c r="G13" s="1" t="inlineStr"/>
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œfor am</t>
-        </is>
-      </c>
+      <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
@@ -1147,11 +1107,7 @@
       <c r="G14" s="1" t="inlineStr"/>
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œfor reg</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr"/>
       <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
@@ -1190,11 +1146,7 @@
       <c r="G15" s="1" t="inlineStr"/>
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>L51: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œof the</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
       <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
@@ -1233,11 +1185,7 @@
       <c r="G16" s="1" t="inlineStr"/>
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œtherefo</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr"/>
       <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
@@ -1276,11 +1224,7 @@
       <c r="G17" s="1" t="inlineStr"/>
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œto be</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
       <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
@@ -1297,347 +1241,6 @@
       <c r="X17" s="1" t="inlineStr"/>
       <c r="Y17" s="1" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr"/>
-      <c r="B18" s="1" t="inlineStr"/>
-      <c r="C18" s="1" t="inlineStr"/>
-      <c r="D18" s="1" t="inlineStr"/>
-      <c r="E18" s="1" t="inlineStr"/>
-      <c r="F18" s="1" t="inlineStr"/>
-      <c r="G18" s="1" t="inlineStr"/>
-      <c r="H18" s="1" t="inlineStr"/>
-      <c r="I18" s="1" t="inlineStr"/>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L58: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œing int</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr"/>
-      <c r="L18" s="1" t="inlineStr"/>
-      <c r="M18" s="1" t="inlineStr"/>
-      <c r="N18" s="1" t="inlineStr"/>
-      <c r="O18" s="1" t="inlineStr"/>
-      <c r="P18" s="1" t="inlineStr"/>
-      <c r="Q18" s="1" t="inlineStr"/>
-      <c r="R18" s="1" t="inlineStr"/>
-      <c r="S18" s="1" t="inlineStr"/>
-      <c r="T18" s="1" t="inlineStr"/>
-      <c r="U18" s="1" t="inlineStr"/>
-      <c r="V18" s="1" t="inlineStr"/>
-      <c r="W18" s="1" t="inlineStr"/>
-      <c r="X18" s="1" t="inlineStr"/>
-      <c r="Y18" s="1" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr"/>
-      <c r="B19" s="1" t="inlineStr"/>
-      <c r="C19" s="1" t="inlineStr"/>
-      <c r="D19" s="1" t="inlineStr"/>
-      <c r="E19" s="1" t="inlineStr"/>
-      <c r="F19" s="1" t="inlineStr"/>
-      <c r="G19" s="1" t="inlineStr"/>
-      <c r="H19" s="1" t="inlineStr"/>
-      <c r="I19" s="1" t="inlineStr"/>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œsioners</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr"/>
-      <c r="L19" s="1" t="inlineStr"/>
-      <c r="M19" s="1" t="inlineStr"/>
-      <c r="N19" s="1" t="inlineStr"/>
-      <c r="O19" s="1" t="inlineStr"/>
-      <c r="P19" s="1" t="inlineStr"/>
-      <c r="Q19" s="1" t="inlineStr"/>
-      <c r="R19" s="1" t="inlineStr"/>
-      <c r="S19" s="1" t="inlineStr"/>
-      <c r="T19" s="1" t="inlineStr"/>
-      <c r="U19" s="1" t="inlineStr"/>
-      <c r="V19" s="1" t="inlineStr"/>
-      <c r="W19" s="1" t="inlineStr"/>
-      <c r="X19" s="1" t="inlineStr"/>
-      <c r="Y19" s="1" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr"/>
-      <c r="B20" s="1" t="inlineStr"/>
-      <c r="C20" s="1" t="inlineStr"/>
-      <c r="D20" s="1" t="inlineStr"/>
-      <c r="E20" s="1" t="inlineStr"/>
-      <c r="F20" s="1" t="inlineStr"/>
-      <c r="G20" s="1" t="inlineStr"/>
-      <c r="H20" s="1" t="inlineStr"/>
-      <c r="I20" s="1" t="inlineStr"/>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L61: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œsame</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr"/>
-      <c r="L20" s="1" t="inlineStr"/>
-      <c r="M20" s="1" t="inlineStr"/>
-      <c r="N20" s="1" t="inlineStr"/>
-      <c r="O20" s="1" t="inlineStr"/>
-      <c r="P20" s="1" t="inlineStr"/>
-      <c r="Q20" s="1" t="inlineStr"/>
-      <c r="R20" s="1" t="inlineStr"/>
-      <c r="S20" s="1" t="inlineStr"/>
-      <c r="T20" s="1" t="inlineStr"/>
-      <c r="U20" s="1" t="inlineStr"/>
-      <c r="V20" s="1" t="inlineStr"/>
-      <c r="W20" s="1" t="inlineStr"/>
-      <c r="X20" s="1" t="inlineStr"/>
-      <c r="Y20" s="1" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr"/>
-      <c r="B21" s="1" t="inlineStr"/>
-      <c r="C21" s="1" t="inlineStr"/>
-      <c r="D21" s="1" t="inlineStr"/>
-      <c r="E21" s="1" t="inlineStr"/>
-      <c r="F21" s="1" t="inlineStr"/>
-      <c r="G21" s="1" t="inlineStr"/>
-      <c r="H21" s="1" t="inlineStr"/>
-      <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr"/>
-      <c r="L21" s="1" t="inlineStr"/>
-      <c r="M21" s="1" t="inlineStr"/>
-      <c r="N21" s="1" t="inlineStr"/>
-      <c r="O21" s="1" t="inlineStr"/>
-      <c r="P21" s="1" t="inlineStr"/>
-      <c r="Q21" s="1" t="inlineStr"/>
-      <c r="R21" s="1" t="inlineStr"/>
-      <c r="S21" s="1" t="inlineStr"/>
-      <c r="T21" s="1" t="inlineStr"/>
-      <c r="U21" s="1" t="inlineStr"/>
-      <c r="V21" s="1" t="inlineStr"/>
-      <c r="W21" s="1" t="inlineStr"/>
-      <c r="X21" s="1" t="inlineStr"/>
-      <c r="Y21" s="1" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr"/>
-      <c r="B22" s="1" t="inlineStr"/>
-      <c r="C22" s="1" t="inlineStr"/>
-      <c r="D22" s="1" t="inlineStr"/>
-      <c r="E22" s="1" t="inlineStr"/>
-      <c r="F22" s="1" t="inlineStr"/>
-      <c r="G22" s="1" t="inlineStr"/>
-      <c r="H22" s="1" t="inlineStr"/>
-      <c r="I22" s="1" t="inlineStr"/>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L72: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œand</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr"/>
-      <c r="L22" s="1" t="inlineStr"/>
-      <c r="M22" s="1" t="inlineStr"/>
-      <c r="N22" s="1" t="inlineStr"/>
-      <c r="O22" s="1" t="inlineStr"/>
-      <c r="P22" s="1" t="inlineStr"/>
-      <c r="Q22" s="1" t="inlineStr"/>
-      <c r="R22" s="1" t="inlineStr"/>
-      <c r="S22" s="1" t="inlineStr"/>
-      <c r="T22" s="1" t="inlineStr"/>
-      <c r="U22" s="1" t="inlineStr"/>
-      <c r="V22" s="1" t="inlineStr"/>
-      <c r="W22" s="1" t="inlineStr"/>
-      <c r="X22" s="1" t="inlineStr"/>
-      <c r="Y22" s="1" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr"/>
-      <c r="B23" s="1" t="inlineStr"/>
-      <c r="C23" s="1" t="inlineStr"/>
-      <c r="D23" s="1" t="inlineStr"/>
-      <c r="E23" s="1" t="inlineStr"/>
-      <c r="F23" s="1" t="inlineStr"/>
-      <c r="G23" s="1" t="inlineStr"/>
-      <c r="H23" s="1" t="inlineStr"/>
-      <c r="I23" s="1" t="inlineStr"/>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>L74: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œChand</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr"/>
-      <c r="L23" s="1" t="inlineStr"/>
-      <c r="M23" s="1" t="inlineStr"/>
-      <c r="N23" s="1" t="inlineStr"/>
-      <c r="O23" s="1" t="inlineStr"/>
-      <c r="P23" s="1" t="inlineStr"/>
-      <c r="Q23" s="1" t="inlineStr"/>
-      <c r="R23" s="1" t="inlineStr"/>
-      <c r="S23" s="1" t="inlineStr"/>
-      <c r="T23" s="1" t="inlineStr"/>
-      <c r="U23" s="1" t="inlineStr"/>
-      <c r="V23" s="1" t="inlineStr"/>
-      <c r="W23" s="1" t="inlineStr"/>
-      <c r="X23" s="1" t="inlineStr"/>
-      <c r="Y23" s="1" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr"/>
-      <c r="B24" s="1" t="inlineStr"/>
-      <c r="C24" s="1" t="inlineStr"/>
-      <c r="D24" s="1" t="inlineStr"/>
-      <c r="E24" s="1" t="inlineStr"/>
-      <c r="F24" s="1" t="inlineStr"/>
-      <c r="G24" s="1" t="inlineStr"/>
-      <c r="H24" s="1" t="inlineStr"/>
-      <c r="I24" s="1" t="inlineStr"/>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>L75: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œwell in</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr"/>
-      <c r="L24" s="1" t="inlineStr"/>
-      <c r="M24" s="1" t="inlineStr"/>
-      <c r="N24" s="1" t="inlineStr"/>
-      <c r="O24" s="1" t="inlineStr"/>
-      <c r="P24" s="1" t="inlineStr"/>
-      <c r="Q24" s="1" t="inlineStr"/>
-      <c r="R24" s="1" t="inlineStr"/>
-      <c r="S24" s="1" t="inlineStr"/>
-      <c r="T24" s="1" t="inlineStr"/>
-      <c r="U24" s="1" t="inlineStr"/>
-      <c r="V24" s="1" t="inlineStr"/>
-      <c r="W24" s="1" t="inlineStr"/>
-      <c r="X24" s="1" t="inlineStr"/>
-      <c r="Y24" s="1" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr"/>
-      <c r="B25" s="1" t="inlineStr"/>
-      <c r="C25" s="1" t="inlineStr"/>
-      <c r="D25" s="1" t="inlineStr"/>
-      <c r="E25" s="1" t="inlineStr"/>
-      <c r="F25" s="1" t="inlineStr"/>
-      <c r="G25" s="1" t="inlineStr"/>
-      <c r="H25" s="1" t="inlineStr"/>
-      <c r="I25" s="1" t="inlineStr"/>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>L76: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œpractic</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr"/>
-      <c r="L25" s="1" t="inlineStr"/>
-      <c r="M25" s="1" t="inlineStr"/>
-      <c r="N25" s="1" t="inlineStr"/>
-      <c r="O25" s="1" t="inlineStr"/>
-      <c r="P25" s="1" t="inlineStr"/>
-      <c r="Q25" s="1" t="inlineStr"/>
-      <c r="R25" s="1" t="inlineStr"/>
-      <c r="S25" s="1" t="inlineStr"/>
-      <c r="T25" s="1" t="inlineStr"/>
-      <c r="U25" s="1" t="inlineStr"/>
-      <c r="V25" s="1" t="inlineStr"/>
-      <c r="W25" s="1" t="inlineStr"/>
-      <c r="X25" s="1" t="inlineStr"/>
-      <c r="Y25" s="1" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr"/>
-      <c r="B26" s="1" t="inlineStr"/>
-      <c r="C26" s="1" t="inlineStr"/>
-      <c r="D26" s="1" t="inlineStr"/>
-      <c r="E26" s="1" t="inlineStr"/>
-      <c r="F26" s="1" t="inlineStr"/>
-      <c r="G26" s="1" t="inlineStr"/>
-      <c r="H26" s="1" t="inlineStr"/>
-      <c r="I26" s="1" t="inlineStr"/>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œespecia</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr"/>
-      <c r="L26" s="1" t="inlineStr"/>
-      <c r="M26" s="1" t="inlineStr"/>
-      <c r="N26" s="1" t="inlineStr"/>
-      <c r="O26" s="1" t="inlineStr"/>
-      <c r="P26" s="1" t="inlineStr"/>
-      <c r="Q26" s="1" t="inlineStr"/>
-      <c r="R26" s="1" t="inlineStr"/>
-      <c r="S26" s="1" t="inlineStr"/>
-      <c r="T26" s="1" t="inlineStr"/>
-      <c r="U26" s="1" t="inlineStr"/>
-      <c r="V26" s="1" t="inlineStr"/>
-      <c r="W26" s="1" t="inlineStr"/>
-      <c r="X26" s="1" t="inlineStr"/>
-      <c r="Y26" s="1" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr"/>
-      <c r="B27" s="1" t="inlineStr"/>
-      <c r="C27" s="1" t="inlineStr"/>
-      <c r="D27" s="1" t="inlineStr"/>
-      <c r="E27" s="1" t="inlineStr"/>
-      <c r="F27" s="1" t="inlineStr"/>
-      <c r="G27" s="1" t="inlineStr"/>
-      <c r="H27" s="1" t="inlineStr"/>
-      <c r="I27" s="1" t="inlineStr"/>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œamina</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr"/>
-      <c r="L27" s="1" t="inlineStr"/>
-      <c r="M27" s="1" t="inlineStr"/>
-      <c r="N27" s="1" t="inlineStr"/>
-      <c r="O27" s="1" t="inlineStr"/>
-      <c r="P27" s="1" t="inlineStr"/>
-      <c r="Q27" s="1" t="inlineStr"/>
-      <c r="R27" s="1" t="inlineStr"/>
-      <c r="S27" s="1" t="inlineStr"/>
-      <c r="T27" s="1" t="inlineStr"/>
-      <c r="U27" s="1" t="inlineStr"/>
-      <c r="V27" s="1" t="inlineStr"/>
-      <c r="W27" s="1" t="inlineStr"/>
-      <c r="X27" s="1" t="inlineStr"/>
-      <c r="Y27" s="1" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr"/>
-      <c r="B28" s="1" t="inlineStr"/>
-      <c r="C28" s="1" t="inlineStr"/>
-      <c r="D28" s="1" t="inlineStr"/>
-      <c r="E28" s="1" t="inlineStr"/>
-      <c r="F28" s="1" t="inlineStr"/>
-      <c r="G28" s="1" t="inlineStr"/>
-      <c r="H28" s="1" t="inlineStr"/>
-      <c r="I28" s="1" t="inlineStr"/>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t>L81: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œalso t</t>
-        </is>
-      </c>
-      <c r="K28" s="1" t="inlineStr"/>
-      <c r="L28" s="1" t="inlineStr"/>
-      <c r="M28" s="1" t="inlineStr"/>
-      <c r="N28" s="1" t="inlineStr"/>
-      <c r="O28" s="1" t="inlineStr"/>
-      <c r="P28" s="1" t="inlineStr"/>
-      <c r="Q28" s="1" t="inlineStr"/>
-      <c r="R28" s="1" t="inlineStr"/>
-      <c r="S28" s="1" t="inlineStr"/>
-      <c r="T28" s="1" t="inlineStr"/>
-      <c r="U28" s="1" t="inlineStr"/>
-      <c r="V28" s="1" t="inlineStr"/>
-      <c r="W28" s="1" t="inlineStr"/>
-      <c r="X28" s="1" t="inlineStr"/>
-      <c r="Y28" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
